--- a/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 12,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,06</t>
+          <t>0,22; 2,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,53</t>
+          <t>0,3; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,25</t>
+          <t>0,65; 4,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,35</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,67</t>
+          <t>0,56; 3,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,72</t>
+          <t>0,29; 2,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,2</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,27</t>
+          <t>0,13; 1,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,51</t>
+          <t>0,75; 2,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,69</t>
+          <t>0,62; 2,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,93</t>
+          <t>1,04; 9,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,91</t>
+          <t>0,89; 5,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,38</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 11,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,53</t>
+          <t>0,0; 15,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,4</t>
+          <t>0,33; 3,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,36</t>
+          <t>0,72; 3,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,26</t>
+          <t>0,36; 2,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,57</t>
+          <t>1,15; 9,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 10,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,15</t>
+          <t>1,31; 7,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,76</t>
+          <t>0,15; 1,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,89</t>
+          <t>0,87; 3,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,87</t>
+          <t>0,83; 14,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,22; 1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,33; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,18</t>
+          <t>0,59; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,0</t>
+          <t>0,79; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,22; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,87</t>
+          <t>0,6; 1,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,46</t>
+          <t>0,83; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,85</t>
+          <t>1,7; 9,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,08</t>
+          <t>0,3; 1,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,51</t>
+          <t>0,63; 1,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,89</t>
+          <t>0,87; 1,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,5</t>
+          <t>1,89; 6,48</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3787</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2720</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2046</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2633</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4506</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1863</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2872</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3287</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>542; 5109</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2606</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4359</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2285</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5934</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2990</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>649; 6024</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1247; 8431</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3982</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4189</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1422; 9142</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>674; 6487</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3707</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>596; 5255</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3524; 11564</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2672; 11533</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>645; 6036</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2457</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5160</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1330; 8056</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>631; 6224</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3489</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5630</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5311</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3562</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5881</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>734; 7278</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2171; 9997</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1203; 6933</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>785; 6736</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5240</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4331</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2635</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4061</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1918; 10806</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7283</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>484; 5773</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4022</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2592; 11730</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>555; 9678</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16946</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8076</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2190; 10369</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3753; 12783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>797; 6287</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1380; 8572</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4266; 14013</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5530; 16171</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2233; 12147</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3656; 13131</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8696; 20149</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11414; 25473</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4383; 15019</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,56</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,22 +742,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,09</t>
+          <t>0,22; 2,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 8,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,74</t>
+          <t>0,29; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,39</t>
+          <t>0,66; 4,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 12,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,63</t>
+          <t>0,82; 3,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,75</t>
+          <t>0,28; 2,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 13,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,13</t>
+          <t>0,13; 1,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,45</t>
+          <t>0,71; 2,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,69</t>
+          <t>0,6; 2,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,75</t>
+          <t>1,01; 9,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,36</t>
+          <t>0,83; 5,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,67</t>
+          <t>0,37; 3,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,95</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,29</t>
+          <t>0,33; 3,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,33</t>
+          <t>0,71; 3,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,05</t>
+          <t>0,34; 2,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,88</t>
+          <t>1,13; 10,35</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,74</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,36</t>
+          <t>1,45; 7,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,77</t>
+          <t>0,15; 1,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,93</t>
+          <t>0,94; 3,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 14,43</t>
+          <t>0,81; 12,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,35</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,41; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,0</t>
+          <t>0,58; 2,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,27</t>
+          <t>1,15; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,37</t>
+          <t>0,19; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,98</t>
+          <t>0,58; 1,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,41</t>
+          <t>0,75; 2,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,23</t>
+          <t>1,81; 9,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,08</t>
+          <t>0,31; 1,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,47</t>
+          <t>0,62; 1,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,94</t>
+          <t>0,84; 1,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,48</t>
+          <t>1,85; 6,4</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3787</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2720</t>
+          <t>0; 3127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2633</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4506</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1863</t>
+          <t>0; 1828</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 3532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3287</t>
+          <t>0; 3283</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>542; 5109</t>
+          <t>542; 4911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 3092</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>649; 6024</t>
+          <t>648; 5581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1247; 8431</t>
+          <t>1273; 8435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3982</t>
+          <t>0; 3583</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4189</t>
+          <t>0; 4193</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1422; 9142</t>
+          <t>2059; 9426</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>674; 6487</t>
+          <t>666; 6161</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3707</t>
+          <t>0; 4400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>596; 5255</t>
+          <t>598; 5877</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3524; 11564</t>
+          <t>3358; 11921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2672; 11533</t>
+          <t>2550; 12001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>645; 6036</t>
+          <t>627; 5653</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5160</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1330; 8056</t>
+          <t>1253; 7692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631; 6224</t>
+          <t>625; 6180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5630</t>
+          <t>0; 4820</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 5328</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3562</t>
+          <t>0; 3589</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5881</t>
+          <t>0; 5731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>734; 7278</t>
+          <t>728; 6834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2171; 9997</t>
+          <t>2120; 9602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1203; 6933</t>
+          <t>1164; 6892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>785; 6736</t>
+          <t>771; 7054</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2279,52 +2279,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 3798</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2635</t>
+          <t>0; 2915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 3555</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 4513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1918; 10806</t>
+          <t>2124; 10922</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7283</t>
+          <t>0; 9092</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484; 5773</t>
+          <t>482; 6139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4022</t>
+          <t>0; 4573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2592; 11730</t>
+          <t>2795; 11859</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>555; 9678</t>
+          <t>546; 8227</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1320; 8076</t>
+          <t>1329; 8387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2190; 10369</t>
+          <t>2710; 10542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3753; 12783</t>
+          <t>3692; 13046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>797; 6287</t>
+          <t>1150; 6645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1380; 8572</t>
+          <t>1172; 8518</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4266; 14013</t>
+          <t>4112; 14009</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5530; 16171</t>
+          <t>5013; 16009</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2233; 12147</t>
+          <t>2388; 12110</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656; 13131</t>
+          <t>3832; 13324</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8696; 20149</t>
+          <t>8545; 20865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11414; 25473</t>
+          <t>10957; 25045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4383; 15019</t>
+          <t>4295; 14847</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,56</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,36</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,82</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,46</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,47</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,49</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,01</t>
+          <t>0,22; 2,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,54</t>
+          <t>0,6; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,39</t>
+          <t>0,28; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,71</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,74</t>
+          <t>0,29; 2,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,61</t>
+          <t>0,64; 4,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,05</t>
+          <t>0,0; 13,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,13; 1,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,53</t>
+          <t>0,64; 2,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,8</t>
+          <t>0,6; 2,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,13</t>
+          <t>1,04; 9,7</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,12</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,65</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>0,0; 19,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,83; 4,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,37; 3,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,09</t>
+          <t>0,33; 3,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,2</t>
+          <t>0,69; 3,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,04</t>
+          <t>0,36; 2,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,35</t>
+          <t>1,33; 11,42</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,82</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,53; 7,15</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,45</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,11</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,5</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,89</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,13</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,77</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,44</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,88</t>
+          <t>0,15; 1,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,97</t>
+          <t>0,85; 3,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 12,27</t>
+          <t>0,75; 14,4</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,59</t>
+          <t>0,58; 1,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,04</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,62</t>
+          <t>2,0; 10,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,37</t>
+          <t>0,24; 1,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,98</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,39</t>
+          <t>0,65; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,2</t>
+          <t>1,0; 7,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,09</t>
+          <t>0,31; 1,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,52</t>
+          <t>0,61; 1,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,91</t>
+          <t>0,83; 1,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,4</t>
+          <t>2,07; 6,8</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,54 +1577,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>544</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1830</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>657</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3562</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3272</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4194</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1436</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2866</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3127</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2032</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3544</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 3586</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1828</t>
+          <t>0; 1807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 3942</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>542; 4911</t>
+          <t>544; 5039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3092</t>
+          <t>0; 2205</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2285</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2059</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3650</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2185</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>0; 4851</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>648; 5581</t>
+          <t>1503; 9254</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1273; 8435</t>
+          <t>670; 6421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 4197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2059; 9426</t>
+          <t>648; 5554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>666; 6161</t>
+          <t>1233; 8168</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4400</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>598; 5877</t>
+          <t>597; 5922</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3358; 11921</t>
+          <t>3014; 11846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2550; 12001</t>
+          <t>2573; 11501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>627; 5653</t>
+          <t>565; 5292</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3553</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>860</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2772</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>0; 4768</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1253; 7692</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>625; 6180</t>
+          <t>0; 3646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 6800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 5253</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5328</t>
+          <t>1248; 7378</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3589</t>
+          <t>631; 5729</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5731</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>728; 6834</t>
+          <t>728; 7514</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2120; 9602</t>
+          <t>2073; 10090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1164; 6892</t>
+          <t>1220; 7651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>771; 7054</t>
+          <t>863; 7438</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,54 +2201,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5240</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2164</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>6012</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2643</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4789</t>
+          <t>0; 4108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0; 4593</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2253; 10502</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 9352</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3798</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2915</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3555</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4513</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2124; 10922</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 9092</t>
+          <t>0; 2554</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>482; 6139</t>
+          <t>483; 5739</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4573</t>
+          <t>0; 5296</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2795; 11859</t>
+          <t>2542; 11625</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>546; 8227</t>
+          <t>505; 9670</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1329; 8387</t>
+          <t>1386; 8710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2710; 10542</t>
+          <t>4125; 13234</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3692; 13046</t>
+          <t>5075; 16503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1150; 6645</t>
+          <t>2435; 12689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1172; 8518</t>
+          <t>1435; 8668</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4112; 14009</t>
+          <t>2631; 10814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5013; 16009</t>
+          <t>4139; 13964</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2388; 12110</t>
+          <t>952; 7018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3832; 13324</t>
+          <t>3768; 13215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8545; 20865</t>
+          <t>8313; 20692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10957; 25045</t>
+          <t>10889; 24821</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4295; 14847</t>
+          <t>4507; 14770</t>
         </is>
       </c>
     </row>
